--- a/data/mapas/Mapa_de_Carrera_Italiano.xlsx
+++ b/data/mapas/Mapa_de_Carrera_Italiano.xlsx
@@ -555,13 +555,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K55"/>
+  <dimension ref="A1:K41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="J2" s="5" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="J3" s="5">
-        <f>COUNTIF(B6:B55, "SI")</f>
+        <f>COUNTIF(B6:B41, "SI")</f>
         <v/>
       </c>
     </row>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="J4" s="5">
-        <f>COUNTIF(C6:C55, "SI")</f>
+        <f>COUNTIF(C6:C41, "SI")</f>
         <v/>
       </c>
     </row>
@@ -667,14 +667,14 @@
         </is>
       </c>
       <c r="J5" s="5">
-        <f>COUNTIF(F6:F55, "ADEUDA FINAL")</f>
+        <f>COUNTIF(F6:F41, "ADEUDA FINAL")</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>Pedagogía</t>
+          <t>Lengua Italiana I</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
@@ -710,14 +710,14 @@
         </is>
       </c>
       <c r="J6" s="12">
-        <f>COUNTIF(B6:B55, "SI")/44</f>
+        <f>COUNTIF(B6:B41, "SI")/32</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>Didáctica General</t>
+          <t>Fonética y Fonología Italiana I</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
@@ -753,14 +753,14 @@
         </is>
       </c>
       <c r="J7" s="12">
-        <f>COUNTIF(C6:C55, "SI")/44</f>
+        <f>COUNTIF(C6:C41, "SI")/32</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Introducción a la Disciplina</t>
+          <t>Gramática Italiana I</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
@@ -794,7 +794,7 @@
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Práctica Docente I</t>
+          <t>Práctica de Laboratorio y Dicción I</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
@@ -831,10 +831,37 @@
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>📌 2° AÑO</t>
-        </is>
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>Cultura y Civilización Italiana I</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>1° Año</t>
+        </is>
+      </c>
+      <c r="E10" s="10">
+        <f>IF(B10="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F10" s="10">
+        <f>IF(C10="SI", "APROBADO", IF(B10="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G10" s="11">
+        <f>IF(C10="SI", "🟢 Aprobada", IF(B10="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
       <c r="I10" s="14" t="inlineStr">
         <is>
@@ -845,7 +872,7 @@
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>Psicología Educacional</t>
+          <t>Pedagogía</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
@@ -860,7 +887,7 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>2° Año</t>
+          <t>1° Año</t>
         </is>
       </c>
       <c r="E11" s="10">
@@ -884,7 +911,7 @@
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>Sociología de la Educación</t>
+          <t>Lectura, Escritura y Oralidad I (LEO 1)</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
@@ -899,7 +926,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>2° Año</t>
+          <t>1° Año</t>
         </is>
       </c>
       <c r="E12" s="10">
@@ -923,7 +950,7 @@
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>Sujetos de la Educación</t>
+          <t>Construcción de la Práctica Docente en Nivel Inicial y Primario I</t>
         </is>
       </c>
       <c r="B13" s="9" t="inlineStr">
@@ -938,7 +965,7 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>2° Año</t>
+          <t>1° Año</t>
         </is>
       </c>
       <c r="E13" s="10">
@@ -960,49 +987,49 @@
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>Práctica Docente II</t>
-        </is>
-      </c>
-      <c r="B14" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D14" s="10" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>📌 2° AÑO</t>
+        </is>
+      </c>
+      <c r="I14" s="14" t="inlineStr">
+        <is>
+          <t>5. El panel lateral calcula tu avance y porcentaje de carrera en vivo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>Lengua Italiana II</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
         <is>
           <t>2° Año</t>
         </is>
       </c>
-      <c r="E14" s="10">
-        <f>IF(B14="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F14" s="10">
-        <f>IF(C14="SI", "APROBADO", IF(B14="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G14" s="11">
-        <f>IF(C14="SI", "🟢 Aprobada", IF(B14="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-      <c r="I14" s="14" t="inlineStr">
-        <is>
-          <t>5. El panel lateral calcula tu avance y porcentaje de carrera en vivo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>📌 3° AÑO</t>
-        </is>
+      <c r="E15" s="10">
+        <f>IF(B15="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F15" s="10">
+        <f>IF(C15="SI", "APROBADO", IF(B15="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G15" s="11">
+        <f>IF(C15="SI", "🟢 Aprobada", IF(B15="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
       <c r="I15" s="14" t="inlineStr">
         <is>
@@ -1013,7 +1040,7 @@
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>Historia Social de la Educación</t>
+          <t>Fonética y Fonología Italiana II</t>
         </is>
       </c>
       <c r="B16" s="9" t="inlineStr">
@@ -1028,7 +1055,7 @@
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E16" s="10">
@@ -1047,7 +1074,7 @@
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>Residencia I</t>
+          <t>Gramática Italiana II</t>
         </is>
       </c>
       <c r="B17" s="9" t="inlineStr">
@@ -1062,7 +1089,7 @@
       </c>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E17" s="10">
@@ -1081,7 +1108,7 @@
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>Espacio de Definición Institucional</t>
+          <t>Literatura Italiana I (Orígenes, Dante, Petrarca, Boccaccio)</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
@@ -1096,7 +1123,7 @@
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E18" s="10">
@@ -1115,7 +1142,7 @@
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>Práctica Docente III</t>
+          <t>Cultura y Civilización Italiana II</t>
         </is>
       </c>
       <c r="B19" s="9" t="inlineStr">
@@ -1130,7 +1157,7 @@
       </c>
       <c r="D19" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E19" s="10">
@@ -1146,17 +1173,44 @@
         <v/>
       </c>
     </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>📌 4° AÑO</t>
-        </is>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>Didáctica General</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>2° Año</t>
+        </is>
+      </c>
+      <c r="E20" s="10">
+        <f>IF(B20="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F20" s="10">
+        <f>IF(C20="SI", "APROBADO", IF(B20="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G20" s="11">
+        <f>IF(C20="SI", "🟢 Aprobada", IF(B20="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>Residencia II / Taller de Cierre</t>
+          <t>Psicología Educacional</t>
         </is>
       </c>
       <c r="B21" s="9" t="inlineStr">
@@ -1171,7 +1225,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E21" s="10">
@@ -1190,7 +1244,7 @@
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>Ética y Trabajo Docente</t>
+          <t>Sujetos de la Educación</t>
         </is>
       </c>
       <c r="B22" s="9" t="inlineStr">
@@ -1205,7 +1259,7 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E22" s="10">
@@ -1224,7 +1278,7 @@
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>Investigación Educativa</t>
+          <t>Construcción de la Práctica Docente en Nivel Inicial y Primario II y Residencia</t>
         </is>
       </c>
       <c r="B23" s="9" t="inlineStr">
@@ -1239,7 +1293,7 @@
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E23" s="10">
@@ -1255,51 +1309,51 @@
         <v/>
       </c>
     </row>
-    <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="8" t="inlineStr">
-        <is>
-          <t>Práctica Docente IV</t>
-        </is>
-      </c>
-      <c r="B24" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C24" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D24" s="10" t="inlineStr">
-        <is>
-          <t>4° Año</t>
-        </is>
-      </c>
-      <c r="E24" s="10">
-        <f>IF(B24="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F24" s="10">
-        <f>IF(C24="SI", "APROBADO", IF(B24="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G24" s="11">
-        <f>IF(C24="SI", "🟢 Aprobada", IF(B24="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>📌 5° AÑO (NIVEL SUPERIOR / TRAMO SUPERIOR)</t>
-        </is>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>📌 3° AÑO</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>Lengua Italiana III</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr">
+        <is>
+          <t>3° Año</t>
+        </is>
+      </c>
+      <c r="E25" s="10">
+        <f>IF(B25="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F25" s="10">
+        <f>IF(C25="SI", "APROBADO", IF(B25="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G25" s="11">
+        <f>IF(C25="SI", "🟢 Aprobada", IF(B25="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>Seminario de Especialización Superior I</t>
+          <t>Lingüística Aplicada al Italiano</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
@@ -1314,7 +1368,7 @@
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>5° Año (Nivel Superior / Tramo Superior)</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E26" s="10">
@@ -1333,7 +1387,7 @@
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>Taller de Investigación Aplicada</t>
+          <t>Literatura Italiana II (Del Renacimiento al Romanticismo)</t>
         </is>
       </c>
       <c r="B27" s="9" t="inlineStr">
@@ -1348,7 +1402,7 @@
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>5° Año (Nivel Superior / Tramo Superior)</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E27" s="10">
@@ -1367,7 +1421,7 @@
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>Didáctica de Nivel Superior</t>
+          <t>Didáctica Especial y Construcción de la Práctica Docente en Nivel Medio I</t>
         </is>
       </c>
       <c r="B28" s="9" t="inlineStr">
@@ -1382,7 +1436,7 @@
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>5° Año (Nivel Superior / Tramo Superior)</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E28" s="10">
@@ -1401,7 +1455,7 @@
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>Práctica de Nivel Superior I</t>
+          <t>Historia Social de la Educación</t>
         </is>
       </c>
       <c r="B29" s="9" t="inlineStr">
@@ -1416,7 +1470,7 @@
       </c>
       <c r="D29" s="10" t="inlineStr">
         <is>
-          <t>5° Año (Nivel Superior / Tramo Superior)</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E29" s="10">
@@ -1432,51 +1486,51 @@
         <v/>
       </c>
     </row>
-    <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>📌 6° AÑO (NIVEL SUPERIOR / TRAMO SUPERIOR)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="8" t="inlineStr">
-        <is>
-          <t>Seminario de Especialización Superior II</t>
-        </is>
-      </c>
-      <c r="B31" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C31" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D31" s="10" t="inlineStr">
-        <is>
-          <t>6° Año (Nivel Superior / Tramo Superior)</t>
-        </is>
-      </c>
-      <c r="E31" s="10">
-        <f>IF(B31="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F31" s="10">
-        <f>IF(C31="SI", "APROBADO", IF(B31="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G31" s="11">
-        <f>IF(C31="SI", "🟢 Aprobada", IF(B31="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>Derechos Humanos, Sociedad y Estado</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="inlineStr">
+        <is>
+          <t>3° Año</t>
+        </is>
+      </c>
+      <c r="E30" s="10">
+        <f>IF(B30="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F30" s="10">
+        <f>IF(C30="SI", "APROBADO", IF(B30="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G30" s="11">
+        <f>IF(C30="SI", "🟢 Aprobada", IF(B30="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>📌 4° AÑO</t>
+        </is>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>Tesis / Trabajo Final de Licenciatura</t>
+          <t>Lengua Italiana IV</t>
         </is>
       </c>
       <c r="B32" s="9" t="inlineStr">
@@ -1491,7 +1545,7 @@
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>6° Año (Nivel Superior / Tramo Superior)</t>
+          <t>4° Año</t>
         </is>
       </c>
       <c r="E32" s="10">
@@ -1510,7 +1564,7 @@
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>Práctica de Nivel Superior II</t>
+          <t>Literatura Italiana Contemporánea (Siglos XX y XXI)</t>
         </is>
       </c>
       <c r="B33" s="9" t="inlineStr">
@@ -1525,7 +1579,7 @@
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>6° Año (Nivel Superior / Tramo Superior)</t>
+          <t>4° Año</t>
         </is>
       </c>
       <c r="E33" s="10">
@@ -1544,7 +1598,7 @@
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>Acreditación de Residencia Superior</t>
+          <t>Estudios Culturales de Italia y la Emigración Italiana en Argentina</t>
         </is>
       </c>
       <c r="B34" s="9" t="inlineStr">
@@ -1559,7 +1613,7 @@
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>6° Año (Nivel Superior / Tramo Superior)</t>
+          <t>4° Año</t>
         </is>
       </c>
       <c r="E34" s="10">
@@ -1575,17 +1629,44 @@
         <v/>
       </c>
     </row>
-    <row r="35" ht="22" customHeight="1">
-      <c r="A35" s="7" t="inlineStr">
-        <is>
-          <t>📌 GENERAL / OPTATIVAS</t>
-        </is>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>Didáctica Especial y Residencia en Nivel Medio y Superior</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D35" s="10" t="inlineStr">
+        <is>
+          <t>4° Año</t>
+        </is>
+      </c>
+      <c r="E35" s="10">
+        <f>IF(B35="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F35" s="10">
+        <f>IF(C35="SI", "APROBADO", IF(B35="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G35" s="11">
+        <f>IF(C35="SI", "🟢 Aprobada", IF(B35="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>CONST.Práctica DOCENTE NIVEL SUPERIOR</t>
+          <t>Educación Sexual Integral (ESI)</t>
         </is>
       </c>
       <c r="B36" s="9" t="inlineStr">
@@ -1600,7 +1681,7 @@
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
-          <t>General / Optativas</t>
+          <t>4° Año</t>
         </is>
       </c>
       <c r="E36" s="10">
@@ -1619,7 +1700,7 @@
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>Derechos Humanos Soc y Estado</t>
+          <t>Ética y Trabajo Docente</t>
         </is>
       </c>
       <c r="B37" s="9" t="inlineStr">
@@ -1634,7 +1715,7 @@
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>General / Optativas</t>
+          <t>4° Año</t>
         </is>
       </c>
       <c r="E37" s="10">
@@ -1650,44 +1731,17 @@
         <v/>
       </c>
     </row>
-    <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="8" t="inlineStr">
-        <is>
-          <t>Fonética Y Fonología I</t>
-        </is>
-      </c>
-      <c r="B38" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C38" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D38" s="10" t="inlineStr">
-        <is>
-          <t>General / Optativas</t>
-        </is>
-      </c>
-      <c r="E38" s="10">
-        <f>IF(B38="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F38" s="10">
-        <f>IF(C38="SI", "APROBADO", IF(B38="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G38" s="11">
-        <f>IF(C38="SI", "🟢 Aprobada", IF(B38="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>📌 TRAMO SUPERIOR / SEMINARIOS</t>
+        </is>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>Fonética Y Fonología II</t>
+          <t>Seminario de Literatura Italiana y Traducción</t>
         </is>
       </c>
       <c r="B39" s="9" t="inlineStr">
@@ -1702,7 +1756,7 @@
       </c>
       <c r="D39" s="10" t="inlineStr">
         <is>
-          <t>General / Optativas</t>
+          <t>Tramo Superior / Seminarios</t>
         </is>
       </c>
       <c r="E39" s="10">
@@ -1721,7 +1775,7 @@
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>Historia de la Lengua Italiana</t>
+          <t>Seminario de Didáctica del Italiano como Lengua Extranjera</t>
         </is>
       </c>
       <c r="B40" s="9" t="inlineStr">
@@ -1736,7 +1790,7 @@
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t>General / Optativas</t>
+          <t>Tramo Superior / Seminarios</t>
         </is>
       </c>
       <c r="E40" s="10">
@@ -1755,7 +1809,7 @@
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>Historia Romana y Medieval</t>
+          <t>Taller de Cultura y Cine Italiano</t>
         </is>
       </c>
       <c r="B41" s="9" t="inlineStr">
@@ -1770,7 +1824,7 @@
       </c>
       <c r="D41" s="10" t="inlineStr">
         <is>
-          <t>General / Optativas</t>
+          <t>Tramo Superior / Seminarios</t>
         </is>
       </c>
       <c r="E41" s="10">
@@ -1786,504 +1840,26 @@
         <v/>
       </c>
     </row>
-    <row r="42" ht="20" customHeight="1">
-      <c r="A42" s="8" t="inlineStr">
-        <is>
-          <t>La Ens. del Ital. a Partir del Arte Italiano</t>
-        </is>
-      </c>
-      <c r="B42" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C42" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D42" s="10" t="inlineStr">
-        <is>
-          <t>General / Optativas</t>
-        </is>
-      </c>
-      <c r="E42" s="10">
-        <f>IF(B42="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F42" s="10">
-        <f>IF(C42="SI", "APROBADO", IF(B42="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G42" s="11">
-        <f>IF(C42="SI", "🟢 Aprobada", IF(B42="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43" ht="20" customHeight="1">
-      <c r="A43" s="8" t="inlineStr">
-        <is>
-          <t>La Ens. del Italiano a Partir del Cine</t>
-        </is>
-      </c>
-      <c r="B43" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C43" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D43" s="10" t="inlineStr">
-        <is>
-          <t>General / Optativas</t>
-        </is>
-      </c>
-      <c r="E43" s="10">
-        <f>IF(B43="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F43" s="10">
-        <f>IF(C43="SI", "APROBADO", IF(B43="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G43" s="11">
-        <f>IF(C43="SI", "🟢 Aprobada", IF(B43="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="8" t="inlineStr">
-        <is>
-          <t>La Ens. del Italiano y la Divina Comedia I</t>
-        </is>
-      </c>
-      <c r="B44" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C44" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D44" s="10" t="inlineStr">
-        <is>
-          <t>General / Optativas</t>
-        </is>
-      </c>
-      <c r="E44" s="10">
-        <f>IF(B44="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F44" s="10">
-        <f>IF(C44="SI", "APROBADO", IF(B44="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G44" s="11">
-        <f>IF(C44="SI", "🟢 Aprobada", IF(B44="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="8" t="inlineStr">
-        <is>
-          <t>La Ens. del Italiano y la Divina Comedia II</t>
-        </is>
-      </c>
-      <c r="B45" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C45" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D45" s="10" t="inlineStr">
-        <is>
-          <t>General / Optativas</t>
-        </is>
-      </c>
-      <c r="E45" s="10">
-        <f>IF(B45="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F45" s="10">
-        <f>IF(C45="SI", "APROBADO", IF(B45="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G45" s="11">
-        <f>IF(C45="SI", "🟢 Aprobada", IF(B45="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="8" t="inlineStr">
-        <is>
-          <t>La Enseñanza del Italiano a Partir de las Culturas Regionales</t>
-        </is>
-      </c>
-      <c r="B46" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C46" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D46" s="10" t="inlineStr">
-        <is>
-          <t>General / Optativas</t>
-        </is>
-      </c>
-      <c r="E46" s="10">
-        <f>IF(B46="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F46" s="10">
-        <f>IF(C46="SI", "APROBADO", IF(B46="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G46" s="11">
-        <f>IF(C46="SI", "🟢 Aprobada", IF(B46="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47" ht="20" customHeight="1">
-      <c r="A47" s="8" t="inlineStr">
-        <is>
-          <t>Latin I</t>
-        </is>
-      </c>
-      <c r="B47" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C47" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D47" s="10" t="inlineStr">
-        <is>
-          <t>General / Optativas</t>
-        </is>
-      </c>
-      <c r="E47" s="10">
-        <f>IF(B47="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F47" s="10">
-        <f>IF(C47="SI", "APROBADO", IF(B47="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G47" s="11">
-        <f>IF(C47="SI", "🟢 Aprobada", IF(B47="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48" ht="20" customHeight="1">
-      <c r="A48" s="8" t="inlineStr">
-        <is>
-          <t>LENGUA EXTRANJERA Francés I</t>
-        </is>
-      </c>
-      <c r="B48" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C48" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D48" s="10" t="inlineStr">
-        <is>
-          <t>General / Optativas</t>
-        </is>
-      </c>
-      <c r="E48" s="10">
-        <f>IF(B48="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F48" s="10">
-        <f>IF(C48="SI", "APROBADO", IF(B48="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G48" s="11">
-        <f>IF(C48="SI", "🟢 Aprobada", IF(B48="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49" ht="20" customHeight="1">
-      <c r="A49" s="8" t="inlineStr">
-        <is>
-          <t>Lengua Italiana I</t>
-        </is>
-      </c>
-      <c r="B49" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C49" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D49" s="10" t="inlineStr">
-        <is>
-          <t>General / Optativas</t>
-        </is>
-      </c>
-      <c r="E49" s="10">
-        <f>IF(B49="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F49" s="10">
-        <f>IF(C49="SI", "APROBADO", IF(B49="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G49" s="11">
-        <f>IF(C49="SI", "🟢 Aprobada", IF(B49="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50" ht="20" customHeight="1">
-      <c r="A50" s="8" t="inlineStr">
-        <is>
-          <t>Lengua Italiana II</t>
-        </is>
-      </c>
-      <c r="B50" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C50" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D50" s="10" t="inlineStr">
-        <is>
-          <t>General / Optativas</t>
-        </is>
-      </c>
-      <c r="E50" s="10">
-        <f>IF(B50="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F50" s="10">
-        <f>IF(C50="SI", "APROBADO", IF(B50="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G50" s="11">
-        <f>IF(C50="SI", "🟢 Aprobada", IF(B50="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51" ht="20" customHeight="1">
-      <c r="A51" s="8" t="inlineStr">
-        <is>
-          <t>Lengua Italiana III</t>
-        </is>
-      </c>
-      <c r="B51" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C51" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D51" s="10" t="inlineStr">
-        <is>
-          <t>General / Optativas</t>
-        </is>
-      </c>
-      <c r="E51" s="10">
-        <f>IF(B51="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F51" s="10">
-        <f>IF(C51="SI", "APROBADO", IF(B51="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G51" s="11">
-        <f>IF(C51="SI", "🟢 Aprobada", IF(B51="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52" ht="20" customHeight="1">
-      <c r="A52" s="8" t="inlineStr">
-        <is>
-          <t>Lengua Italiana IV</t>
-        </is>
-      </c>
-      <c r="B52" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C52" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D52" s="10" t="inlineStr">
-        <is>
-          <t>General / Optativas</t>
-        </is>
-      </c>
-      <c r="E52" s="10">
-        <f>IF(B52="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F52" s="10">
-        <f>IF(C52="SI", "APROBADO", IF(B52="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G52" s="11">
-        <f>IF(C52="SI", "🟢 Aprobada", IF(B52="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53" ht="20" customHeight="1">
-      <c r="A53" s="8" t="inlineStr">
-        <is>
-          <t>LENGUA ITALIANA IV (1º CUATR.)</t>
-        </is>
-      </c>
-      <c r="B53" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C53" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D53" s="10" t="inlineStr">
-        <is>
-          <t>General / Optativas</t>
-        </is>
-      </c>
-      <c r="E53" s="10">
-        <f>IF(B53="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F53" s="10">
-        <f>IF(C53="SI", "APROBADO", IF(B53="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G53" s="11">
-        <f>IF(C53="SI", "🟢 Aprobada", IF(B53="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54" ht="20" customHeight="1">
-      <c r="A54" s="8" t="inlineStr">
-        <is>
-          <t>Literatura Ital. del Romant. y S. Xx</t>
-        </is>
-      </c>
-      <c r="B54" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C54" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D54" s="10" t="inlineStr">
-        <is>
-          <t>General / Optativas</t>
-        </is>
-      </c>
-      <c r="E54" s="10">
-        <f>IF(B54="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F54" s="10">
-        <f>IF(C54="SI", "APROBADO", IF(B54="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G54" s="11">
-        <f>IF(C54="SI", "🟢 Aprobada", IF(B54="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55" ht="20" customHeight="1">
-      <c r="A55" s="8" t="inlineStr">
-        <is>
-          <t>Nuevas Tecnologias</t>
-        </is>
-      </c>
-      <c r="B55" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C55" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D55" s="10" t="inlineStr">
-        <is>
-          <t>General / Optativas</t>
-        </is>
-      </c>
-      <c r="E55" s="10">
-        <f>IF(B55="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F55" s="10">
-        <f>IF(C55="SI", "APROBADO", IF(B55="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G55" s="11">
-        <f>IF(C55="SI", "🟢 Aprobada", IF(B55="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="I14:J14"/>
+  <mergeCells count="15">
+    <mergeCell ref="A14:G14"/>
     <mergeCell ref="I12:J12"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A31:G31"/>
     <mergeCell ref="I15:J15"/>
     <mergeCell ref="I10:J10"/>
-    <mergeCell ref="A35:G35"/>
     <mergeCell ref="I1:K1"/>
     <mergeCell ref="I11:J11"/>
-    <mergeCell ref="A20:G20"/>
-    <mergeCell ref="A30:G30"/>
+    <mergeCell ref="A24:G24"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A15:G15"/>
+    <mergeCell ref="A38:G38"/>
     <mergeCell ref="I13:J13"/>
-    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="I14:J14"/>
     <mergeCell ref="I9:J9"/>
-    <mergeCell ref="A10:G10"/>
     <mergeCell ref="A5:G5"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="B6 B7 B8 B9 B11 B12 B13 B14 B16 B17 B18 B19 B21 B22 B23 B24 B26 B27 B28 B29 B31 B32 B33 B34 B36 B37 B38 B39 B40 B41 B42 B43 B44 B45 B46 B47 B48 B49 B50 B51 B52 B53 B54 B55 C6 C7 C8 C9 C11 C12 C13 C14 C16 C17 C18 C19 C21 C22 C23 C24 C26 C27 C28 C29 C31 C32 C33 C34 C36 C37 C38 C39 C40 C41 C42 C43 C44 C45 C46 C47 C48 C49 C50 C51 C52 C53 C54 C55" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Opción inválida" error="Por favor, elegí 'SI' o 'NO' de la lista desplegable." type="list">
+    <dataValidation sqref="B6 B7 B8 B9 B10 B11 B12 B13 B15 B16 B17 B18 B19 B20 B21 B22 B23 B25 B26 B27 B28 B29 B30 B32 B33 B34 B35 B36 B37 B39 B40 B41 C6 C7 C8 C9 C10 C11 C12 C13 C15 C16 C17 C18 C19 C20 C21 C22 C23 C25 C26 C27 C28 C29 C30 C32 C33 C34 C35 C36 C37 C39 C40 C41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Opción inválida" error="Por favor, elegí 'SI' o 'NO' de la lista desplegable." type="list">
       <formula1>"SI,NO"</formula1>
     </dataValidation>
   </dataValidations>

--- a/data/mapas/Mapa_de_Carrera_Italiano.xlsx
+++ b/data/mapas/Mapa_de_Carrera_Italiano.xlsx
@@ -555,7 +555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K41"/>
+  <dimension ref="A1:K58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="J2" s="5" t="n">
-        <v>32</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="J3" s="5">
-        <f>COUNTIF(B6:B41, "SI")</f>
+        <f>COUNTIF(B6:B58, "SI")</f>
         <v/>
       </c>
     </row>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="J4" s="5">
-        <f>COUNTIF(C6:C41, "SI")</f>
+        <f>COUNTIF(C6:C58, "SI")</f>
         <v/>
       </c>
     </row>
@@ -667,14 +667,14 @@
         </is>
       </c>
       <c r="J5" s="5">
-        <f>COUNTIF(F6:F41, "ADEUDA FINAL")</f>
+        <f>COUNTIF(F6:F58, "ADEUDA FINAL")</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>Lengua Italiana I</t>
+          <t>Lengua italiana 1</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
@@ -710,14 +710,14 @@
         </is>
       </c>
       <c r="J6" s="12">
-        <f>COUNTIF(B6:B41, "SI")/32</f>
+        <f>COUNTIF(B6:B58, "SI")/49</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>Fonética y Fonología Italiana I</t>
+          <t>Gramatica italiana 1</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
@@ -753,14 +753,14 @@
         </is>
       </c>
       <c r="J7" s="12">
-        <f>COUNTIF(C6:C41, "SI")/32</f>
+        <f>COUNTIF(C6:C58, "SI")/49</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Gramática Italiana I</t>
+          <t>Fonterica y fonologia 1</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
@@ -794,7 +794,7 @@
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Práctica de Laboratorio y Dicción I</t>
+          <t>Literatura italiana medieval</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
@@ -833,7 +833,7 @@
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Cultura y Civilización Italiana I</t>
+          <t>Historia Romana y medieval</t>
         </is>
       </c>
       <c r="B10" s="9" t="inlineStr">
@@ -872,7 +872,7 @@
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>Pedagogía</t>
+          <t>La enseñanza del Italiano a partir de las culturas regionales</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
@@ -911,7 +911,7 @@
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>Lectura, Escritura y Oralidad I (LEO 1)</t>
+          <t>La enseñanza del Italiano a partir del cine y teatro italianos</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
@@ -950,7 +950,7 @@
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>Construcción de la Práctica Docente en Nivel Inicial y Primario I</t>
+          <t>Lectura, escritura y oralidad</t>
         </is>
       </c>
       <c r="B13" s="9" t="inlineStr">
@@ -987,10 +987,37 @@
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>📌 2° AÑO</t>
-        </is>
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>Pedagogía</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>1° Año</t>
+        </is>
+      </c>
+      <c r="E14" s="10">
+        <f>IF(B14="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F14" s="10">
+        <f>IF(C14="SI", "APROBADO", IF(B14="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G14" s="11">
+        <f>IF(C14="SI", "🟢 Aprobada", IF(B14="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
       <c r="I14" s="14" t="inlineStr">
         <is>
@@ -1001,7 +1028,7 @@
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>Lengua Italiana II</t>
+          <t>Psicología Educacional</t>
         </is>
       </c>
       <c r="B15" s="9" t="inlineStr">
@@ -1016,7 +1043,7 @@
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>2° Año</t>
+          <t>1° Año</t>
         </is>
       </c>
       <c r="E15" s="10">
@@ -1040,7 +1067,7 @@
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>Fonética y Fonología Italiana II</t>
+          <t>Psicologia y Sujetos del nivel</t>
         </is>
       </c>
       <c r="B16" s="9" t="inlineStr">
@@ -1055,7 +1082,7 @@
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>2° Año</t>
+          <t>1° Año</t>
         </is>
       </c>
       <c r="E16" s="10">
@@ -1074,7 +1101,7 @@
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>Gramática Italiana II</t>
+          <t>Trabajo de Campo I</t>
         </is>
       </c>
       <c r="B17" s="9" t="inlineStr">
@@ -1089,7 +1116,7 @@
       </c>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t>2° Año</t>
+          <t>1° Año</t>
         </is>
       </c>
       <c r="E17" s="10">
@@ -1108,7 +1135,7 @@
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>Literatura Italiana I (Orígenes, Dante, Petrarca, Boccaccio)</t>
+          <t>Taller de consolidacion de la lengua italiana</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
@@ -1123,7 +1150,7 @@
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>2° Año</t>
+          <t>1° Año</t>
         </is>
       </c>
       <c r="E18" s="10">
@@ -1139,44 +1166,17 @@
         <v/>
       </c>
     </row>
-    <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="8" t="inlineStr">
-        <is>
-          <t>Cultura y Civilización Italiana II</t>
-        </is>
-      </c>
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C19" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D19" s="10" t="inlineStr">
-        <is>
-          <t>2° Año</t>
-        </is>
-      </c>
-      <c r="E19" s="10">
-        <f>IF(B19="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F19" s="10">
-        <f>IF(C19="SI", "APROBADO", IF(B19="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G19" s="11">
-        <f>IF(C19="SI", "🟢 Aprobada", IF(B19="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>📌 2° AÑO</t>
+        </is>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>Didáctica General</t>
+          <t>Lengua italiana 2</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
@@ -1210,7 +1210,7 @@
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>Psicología Educacional</t>
+          <t>Gramatica italiana 2</t>
         </is>
       </c>
       <c r="B21" s="9" t="inlineStr">
@@ -1244,7 +1244,7 @@
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>Sujetos de la Educación</t>
+          <t>Fonterica y fonologia 2</t>
         </is>
       </c>
       <c r="B22" s="9" t="inlineStr">
@@ -1278,7 +1278,7 @@
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>Construcción de la Práctica Docente en Nivel Inicial y Primario II y Residencia</t>
+          <t>Literatura del humanismo y del renacimiento</t>
         </is>
       </c>
       <c r="B23" s="9" t="inlineStr">
@@ -1309,17 +1309,44 @@
         <v/>
       </c>
     </row>
-    <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>📌 3° AÑO</t>
-        </is>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>Historia italiana moderna</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>2° Año</t>
+        </is>
+      </c>
+      <c r="E24" s="10">
+        <f>IF(B24="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F24" s="10">
+        <f>IF(C24="SI", "APROBADO", IF(B24="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G24" s="11">
+        <f>IF(C24="SI", "🟢 Aprobada", IF(B24="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>Lengua Italiana III</t>
+          <t>Latin 1</t>
         </is>
       </c>
       <c r="B25" s="9" t="inlineStr">
@@ -1334,7 +1361,7 @@
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E25" s="10">
@@ -1353,7 +1380,7 @@
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>Lingüística Aplicada al Italiano</t>
+          <t>Didactica general</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
@@ -1368,7 +1395,7 @@
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E26" s="10">
@@ -1387,7 +1414,7 @@
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>Literatura Italiana II (Del Renacimiento al Romanticismo)</t>
+          <t>Trabajo de Campo II</t>
         </is>
       </c>
       <c r="B27" s="9" t="inlineStr">
@@ -1402,7 +1429,7 @@
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E27" s="10">
@@ -1421,7 +1448,7 @@
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>Didáctica Especial y Construcción de la Práctica Docente en Nivel Medio I</t>
+          <t>La enseñanza del italiano y la divina comedia 1</t>
         </is>
       </c>
       <c r="B28" s="9" t="inlineStr">
@@ -1436,7 +1463,7 @@
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E28" s="10">
@@ -1455,7 +1482,7 @@
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>Historia Social de la Educación</t>
+          <t>Nuevas tecnologias</t>
         </is>
       </c>
       <c r="B29" s="9" t="inlineStr">
@@ -1470,7 +1497,7 @@
       </c>
       <c r="D29" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E29" s="10">
@@ -1486,51 +1513,51 @@
         <v/>
       </c>
     </row>
-    <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="8" t="inlineStr">
-        <is>
-          <t>Derechos Humanos, Sociedad y Estado</t>
-        </is>
-      </c>
-      <c r="B30" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C30" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D30" s="10" t="inlineStr">
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>📌 3° AÑO</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>Lengua italiana 3</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr">
         <is>
           <t>3° Año</t>
         </is>
       </c>
-      <c r="E30" s="10">
-        <f>IF(B30="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F30" s="10">
-        <f>IF(C30="SI", "APROBADO", IF(B30="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G30" s="11">
-        <f>IF(C30="SI", "🟢 Aprobada", IF(B30="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t>📌 4° AÑO</t>
-        </is>
+      <c r="E31" s="10">
+        <f>IF(B31="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F31" s="10">
+        <f>IF(C31="SI", "APROBADO", IF(B31="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G31" s="11">
+        <f>IF(C31="SI", "🟢 Aprobada", IF(B31="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>Lengua Italiana IV</t>
+          <t>Literatura italiana del barroco y del iluminismo</t>
         </is>
       </c>
       <c r="B32" s="9" t="inlineStr">
@@ -1545,7 +1572,7 @@
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E32" s="10">
@@ -1564,7 +1591,7 @@
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>Literatura Italiana Contemporánea (Siglos XX y XXI)</t>
+          <t>Latin 2</t>
         </is>
       </c>
       <c r="B33" s="9" t="inlineStr">
@@ -1579,7 +1606,7 @@
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E33" s="10">
@@ -1598,7 +1625,7 @@
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>Estudios Culturales de Italia y la Emigración Italiana en Argentina</t>
+          <t>Construcción de la practica docente en el nivel medio</t>
         </is>
       </c>
       <c r="B34" s="9" t="inlineStr">
@@ -1613,7 +1640,7 @@
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E34" s="10">
@@ -1632,7 +1659,7 @@
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>Didáctica Especial y Residencia en Nivel Medio y Superior</t>
+          <t>Filosofía</t>
         </is>
       </c>
       <c r="B35" s="9" t="inlineStr">
@@ -1647,7 +1674,7 @@
       </c>
       <c r="D35" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E35" s="10">
@@ -1666,7 +1693,7 @@
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>Educación Sexual Integral (ESI)</t>
+          <t>Lingüistica</t>
         </is>
       </c>
       <c r="B36" s="9" t="inlineStr">
@@ -1681,7 +1708,7 @@
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E36" s="10">
@@ -1700,7 +1727,7 @@
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>Ética y Trabajo Docente</t>
+          <t>Construcción de la practica docente en el nivel inicial y primario</t>
         </is>
       </c>
       <c r="B37" s="9" t="inlineStr">
@@ -1715,7 +1742,7 @@
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E37" s="10">
@@ -1731,17 +1758,44 @@
         <v/>
       </c>
     </row>
-    <row r="38" ht="22" customHeight="1">
-      <c r="A38" s="7" t="inlineStr">
-        <is>
-          <t>📌 TRAMO SUPERIOR / SEMINARIOS</t>
-        </is>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>La enseñanza del italiano y la divina comedia 2</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D38" s="10" t="inlineStr">
+        <is>
+          <t>3° Año</t>
+        </is>
+      </c>
+      <c r="E38" s="10">
+        <f>IF(B38="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F38" s="10">
+        <f>IF(C38="SI", "APROBADO", IF(B38="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G38" s="11">
+        <f>IF(C38="SI", "🟢 Aprobada", IF(B38="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>Seminario de Literatura Italiana y Traducción</t>
+          <t>Esi</t>
         </is>
       </c>
       <c r="B39" s="9" t="inlineStr">
@@ -1756,7 +1810,7 @@
       </c>
       <c r="D39" s="10" t="inlineStr">
         <is>
-          <t>Tramo Superior / Seminarios</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E39" s="10">
@@ -1772,44 +1826,17 @@
         <v/>
       </c>
     </row>
-    <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="8" t="inlineStr">
-        <is>
-          <t>Seminario de Didáctica del Italiano como Lengua Extranjera</t>
-        </is>
-      </c>
-      <c r="B40" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C40" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D40" s="10" t="inlineStr">
-        <is>
-          <t>Tramo Superior / Seminarios</t>
-        </is>
-      </c>
-      <c r="E40" s="10">
-        <f>IF(B40="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F40" s="10">
-        <f>IF(C40="SI", "APROBADO", IF(B40="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G40" s="11">
-        <f>IF(C40="SI", "🟢 Aprobada", IF(B40="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
+    <row r="40" ht="22" customHeight="1">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>📌 4° AÑO</t>
+        </is>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>Taller de Cultura y Cine Italiano</t>
+          <t>Lengua italina 4</t>
         </is>
       </c>
       <c r="B41" s="9" t="inlineStr">
@@ -1824,7 +1851,7 @@
       </c>
       <c r="D41" s="10" t="inlineStr">
         <is>
-          <t>Tramo Superior / Seminarios</t>
+          <t>4° Año</t>
         </is>
       </c>
       <c r="E41" s="10">
@@ -1840,26 +1867,577 @@
         <v/>
       </c>
     </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t>La enseñanza del italiano a partir del arte italiano</t>
+        </is>
+      </c>
+      <c r="B42" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D42" s="10" t="inlineStr">
+        <is>
+          <t>4° Año</t>
+        </is>
+      </c>
+      <c r="E42" s="10">
+        <f>IF(B42="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F42" s="10">
+        <f>IF(C42="SI", "APROBADO", IF(B42="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G42" s="11">
+        <f>IF(C42="SI", "🟢 Aprobada", IF(B42="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>Residencia en contextos de injerencia profesional / Didáctica especifica 2 y residencia</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D43" s="10" t="inlineStr">
+        <is>
+          <t>4° Año</t>
+        </is>
+      </c>
+      <c r="E43" s="10">
+        <f>IF(B43="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F43" s="10">
+        <f>IF(C43="SI", "APROBADO", IF(B43="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G43" s="11">
+        <f>IF(C43="SI", "🟢 Aprobada", IF(B43="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>Historia de la educación Argentina</t>
+        </is>
+      </c>
+      <c r="B44" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C44" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D44" s="10" t="inlineStr">
+        <is>
+          <t>4° Año</t>
+        </is>
+      </c>
+      <c r="E44" s="10">
+        <f>IF(B44="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F44" s="10">
+        <f>IF(C44="SI", "APROBADO", IF(B44="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G44" s="11">
+        <f>IF(C44="SI", "🟢 Aprobada", IF(B44="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>DDHH, sociedad y estado</t>
+        </is>
+      </c>
+      <c r="B45" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D45" s="10" t="inlineStr">
+        <is>
+          <t>4° Año</t>
+        </is>
+      </c>
+      <c r="E45" s="10">
+        <f>IF(B45="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F45" s="10">
+        <f>IF(C45="SI", "APROBADO", IF(B45="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G45" s="11">
+        <f>IF(C45="SI", "🟢 Aprobada", IF(B45="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="8" t="inlineStr">
+        <is>
+          <t>Sistema y política educativa</t>
+        </is>
+      </c>
+      <c r="B46" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C46" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D46" s="10" t="inlineStr">
+        <is>
+          <t>4° Año</t>
+        </is>
+      </c>
+      <c r="E46" s="10">
+        <f>IF(B46="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F46" s="10">
+        <f>IF(C46="SI", "APROBADO", IF(B46="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G46" s="11">
+        <f>IF(C46="SI", "🟢 Aprobada", IF(B46="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="8" t="inlineStr">
+        <is>
+          <t>Taller de didactica de la fonetica</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C47" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D47" s="10" t="inlineStr">
+        <is>
+          <t>4° Año</t>
+        </is>
+      </c>
+      <c r="E47" s="10">
+        <f>IF(B47="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F47" s="10">
+        <f>IF(C47="SI", "APROBADO", IF(B47="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G47" s="11">
+        <f>IF(C47="SI", "🟢 Aprobada", IF(B47="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="8" t="inlineStr">
+        <is>
+          <t>Lengua extranjera 1</t>
+        </is>
+      </c>
+      <c r="B48" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C48" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D48" s="10" t="inlineStr">
+        <is>
+          <t>4° Año</t>
+        </is>
+      </c>
+      <c r="E48" s="10">
+        <f>IF(B48="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F48" s="10">
+        <f>IF(C48="SI", "APROBADO", IF(B48="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G48" s="11">
+        <f>IF(C48="SI", "🟢 Aprobada", IF(B48="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="8" t="inlineStr">
+        <is>
+          <t>Lengua extranjera 2</t>
+        </is>
+      </c>
+      <c r="B49" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C49" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D49" s="10" t="inlineStr">
+        <is>
+          <t>4° Año</t>
+        </is>
+      </c>
+      <c r="E49" s="10">
+        <f>IF(B49="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F49" s="10">
+        <f>IF(C49="SI", "APROBADO", IF(B49="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G49" s="11">
+        <f>IF(C49="SI", "🟢 Aprobada", IF(B49="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50" ht="22" customHeight="1">
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>📌 5° AÑO</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="8" t="inlineStr">
+        <is>
+          <t>Historia civilización italina del risogimento y siglo xx</t>
+        </is>
+      </c>
+      <c r="B51" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C51" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D51" s="10" t="inlineStr">
+        <is>
+          <t>5° Año</t>
+        </is>
+      </c>
+      <c r="E51" s="10">
+        <f>IF(B51="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F51" s="10">
+        <f>IF(C51="SI", "APROBADO", IF(B51="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G51" s="11">
+        <f>IF(C51="SI", "🟢 Aprobada", IF(B51="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="8" t="inlineStr">
+        <is>
+          <t>Historia de la lengua italiana</t>
+        </is>
+      </c>
+      <c r="B52" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C52" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D52" s="10" t="inlineStr">
+        <is>
+          <t>5° Año</t>
+        </is>
+      </c>
+      <c r="E52" s="10">
+        <f>IF(B52="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F52" s="10">
+        <f>IF(C52="SI", "APROBADO", IF(B52="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G52" s="11">
+        <f>IF(C52="SI", "🟢 Aprobada", IF(B52="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="8" t="inlineStr">
+        <is>
+          <t>La enseñanza del italiano a partir de la musica italiana</t>
+        </is>
+      </c>
+      <c r="B53" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C53" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D53" s="10" t="inlineStr">
+        <is>
+          <t>5° Año</t>
+        </is>
+      </c>
+      <c r="E53" s="10">
+        <f>IF(B53="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F53" s="10">
+        <f>IF(C53="SI", "APROBADO", IF(B53="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G53" s="11">
+        <f>IF(C53="SI", "🟢 Aprobada", IF(B53="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="8" t="inlineStr">
+        <is>
+          <t>Taller de tecnicas de lectocomprensión e investigación</t>
+        </is>
+      </c>
+      <c r="B54" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C54" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D54" s="10" t="inlineStr">
+        <is>
+          <t>5° Año</t>
+        </is>
+      </c>
+      <c r="E54" s="10">
+        <f>IF(B54="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F54" s="10">
+        <f>IF(C54="SI", "APROBADO", IF(B54="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G54" s="11">
+        <f>IF(C54="SI", "🟢 Aprobada", IF(B54="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="8" t="inlineStr">
+        <is>
+          <t>Construcción de la práctica doncete en el nivel superior y residencia en contextos de injerencia profesional</t>
+        </is>
+      </c>
+      <c r="B55" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C55" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D55" s="10" t="inlineStr">
+        <is>
+          <t>5° Año</t>
+        </is>
+      </c>
+      <c r="E55" s="10">
+        <f>IF(B55="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F55" s="10">
+        <f>IF(C55="SI", "APROBADO", IF(B55="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G55" s="11">
+        <f>IF(C55="SI", "🟢 Aprobada", IF(B55="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="8" t="inlineStr">
+        <is>
+          <t>Lengua 5: Sociolingüistica</t>
+        </is>
+      </c>
+      <c r="B56" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C56" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D56" s="10" t="inlineStr">
+        <is>
+          <t>5° Año</t>
+        </is>
+      </c>
+      <c r="E56" s="10">
+        <f>IF(B56="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F56" s="10">
+        <f>IF(C56="SI", "APROBADO", IF(B56="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G56" s="11">
+        <f>IF(C56="SI", "🟢 Aprobada", IF(B56="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="8" t="inlineStr">
+        <is>
+          <t>Taller de la didáctica del italiano en el nivel superior</t>
+        </is>
+      </c>
+      <c r="B57" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C57" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D57" s="10" t="inlineStr">
+        <is>
+          <t>5° Año</t>
+        </is>
+      </c>
+      <c r="E57" s="10">
+        <f>IF(B57="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F57" s="10">
+        <f>IF(C57="SI", "APROBADO", IF(B57="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G57" s="11">
+        <f>IF(C57="SI", "🟢 Aprobada", IF(B57="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="8" t="inlineStr">
+        <is>
+          <t>• Taller de consolidación de la lengua italiana cursan con carácter obligatorio SOLO los ingresantes que hayan aprobado el examen de admisión con 5 (cinco) ó 6 (seis) puntos. Aquellos ingresantres que hayan obtenido 7 (siete) o más puntos estarán en condiciones de acreditar el Taller de consolidación y, por lo tanto, no deberán cursalo (Ver Acta de Acreditación de 2.11.2018).</t>
+        </is>
+      </c>
+      <c r="B58" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C58" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D58" s="10" t="inlineStr">
+        <is>
+          <t>5° Año</t>
+        </is>
+      </c>
+      <c r="E58" s="10">
+        <f>IF(B58="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F58" s="10">
+        <f>IF(C58="SI", "APROBADO", IF(B58="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G58" s="11">
+        <f>IF(C58="SI", "🟢 Aprobada", IF(B58="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A14:G14"/>
     <mergeCell ref="I12:J12"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="A40:G40"/>
     <mergeCell ref="I15:J15"/>
     <mergeCell ref="I10:J10"/>
+    <mergeCell ref="A50:G50"/>
     <mergeCell ref="I1:K1"/>
     <mergeCell ref="I11:J11"/>
-    <mergeCell ref="A24:G24"/>
+    <mergeCell ref="A30:G30"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A38:G38"/>
     <mergeCell ref="I13:J13"/>
     <mergeCell ref="I14:J14"/>
+    <mergeCell ref="A19:G19"/>
     <mergeCell ref="I9:J9"/>
     <mergeCell ref="A5:G5"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="B6 B7 B8 B9 B10 B11 B12 B13 B15 B16 B17 B18 B19 B20 B21 B22 B23 B25 B26 B27 B28 B29 B30 B32 B33 B34 B35 B36 B37 B39 B40 B41 C6 C7 C8 C9 C10 C11 C12 C13 C15 C16 C17 C18 C19 C20 C21 C22 C23 C25 C26 C27 C28 C29 C30 C32 C33 C34 C35 C36 C37 C39 C40 C41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Opción inválida" error="Por favor, elegí 'SI' o 'NO' de la lista desplegable." type="list">
+    <dataValidation sqref="B6 B7 B8 B9 B10 B11 B12 B13 B14 B15 B16 B17 B18 B20 B21 B22 B23 B24 B25 B26 B27 B28 B29 B31 B32 B33 B34 B35 B36 B37 B38 B39 B41 B42 B43 B44 B45 B46 B47 B48 B49 B51 B52 B53 B54 B55 B56 B57 B58 C6 C7 C8 C9 C10 C11 C12 C13 C14 C15 C16 C17 C18 C20 C21 C22 C23 C24 C25 C26 C27 C28 C29 C31 C32 C33 C34 C35 C36 C37 C38 C39 C41 C42 C43 C44 C45 C46 C47 C48 C49 C51 C52 C53 C54 C55 C56 C57 C58" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Opción inválida" error="Por favor, elegí 'SI' o 'NO' de la lista desplegable." type="list">
       <formula1>"SI,NO"</formula1>
     </dataValidation>
   </dataValidations>
